--- a/Outputs/Tests statistiques/Tests relations quanti-quali.xlsx
+++ b/Outputs/Tests statistiques/Tests relations quanti-quali.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="55">
   <si>
     <t>Couple testé</t>
   </si>
@@ -28,97 +28,157 @@
     <t>Décision</t>
   </si>
   <si>
+    <t>age_vehicule_annees x contrat_id</t>
+  </si>
+  <si>
+    <t>duree_garantie_jours x contrat_id</t>
+  </si>
+  <si>
+    <t>places x segment</t>
+  </si>
+  <si>
+    <t>places x contrat_id</t>
+  </si>
+  <si>
+    <t>puissance x contrat_id</t>
+  </si>
+  <si>
+    <t>puissance x segment</t>
+  </si>
+  <si>
+    <t>puissance x type_vehicule</t>
+  </si>
+  <si>
+    <t>places x type_vehicule</t>
+  </si>
+  <si>
+    <t>y_cible x garantie</t>
+  </si>
+  <si>
+    <t>age_vehicule_annees x type_vehicule</t>
+  </si>
+  <si>
+    <t>puissance x typeinter</t>
+  </si>
+  <si>
+    <t>age_vehicule_annees x segment</t>
+  </si>
+  <si>
+    <t>places x typeinter</t>
+  </si>
+  <si>
+    <t>age_vehicule_annees x garantie</t>
+  </si>
+  <si>
+    <t>places x categorie_mère</t>
+  </si>
+  <si>
+    <t>y_cible x contrat_id</t>
+  </si>
+  <si>
     <t>age_vehicule_annees x categorie_mère</t>
   </si>
   <si>
-    <t>age_vehicule_annees x garantie</t>
-  </si>
-  <si>
-    <t>age_vehicule_annees x segment</t>
-  </si>
-  <si>
-    <t>age_vehicule_annees x type_vehicule</t>
+    <t>age_vehicule_annees x typeinter</t>
+  </si>
+  <si>
+    <t>puissance x garantie</t>
+  </si>
+  <si>
+    <t>y_cible x type_vehicule</t>
+  </si>
+  <si>
+    <t>puissance x categorie_mère</t>
+  </si>
+  <si>
+    <t>nb_sinistres x garantie</t>
+  </si>
+  <si>
+    <t>cout_total_sinistres x garantie</t>
+  </si>
+  <si>
+    <t>y_cible x segment</t>
+  </si>
+  <si>
+    <t>duree_garantie_jours x garantie</t>
+  </si>
+  <si>
+    <t>places x garantie</t>
+  </si>
+  <si>
+    <t>duree_garantie_jours x segment</t>
+  </si>
+  <si>
+    <t>duree_garantie_jours x type_vehicule</t>
+  </si>
+  <si>
+    <t>y_cible x typepermis</t>
+  </si>
+  <si>
+    <t>duree_garantie_jours x categorie_mère</t>
+  </si>
+  <si>
+    <t>y_cible x categorie_mère</t>
+  </si>
+  <si>
+    <t>duree_garantie_jours x typeinter</t>
+  </si>
+  <si>
+    <t>nb_sinistres x contrat_id</t>
+  </si>
+  <si>
+    <t>cout_total_sinistres x contrat_id</t>
+  </si>
+  <si>
+    <t>places x typepermis</t>
+  </si>
+  <si>
+    <t>puissance x typepermis</t>
+  </si>
+  <si>
+    <t>cout_total_sinistres x typeinter</t>
+  </si>
+  <si>
+    <t>nb_sinistres x typeinter</t>
   </si>
   <si>
     <t>age_vehicule_annees x typepermis</t>
   </si>
   <si>
-    <t>duree_garantie_jours x categorie_mère</t>
-  </si>
-  <si>
-    <t>duree_garantie_jours x garantie</t>
-  </si>
-  <si>
-    <t>duree_garantie_jours x segment</t>
-  </si>
-  <si>
-    <t>places x type_vehicule</t>
-  </si>
-  <si>
-    <t>duree_garantie_jours x type_vehicule</t>
-  </si>
-  <si>
-    <t>places x segment</t>
-  </si>
-  <si>
-    <t>places x categorie_mère</t>
-  </si>
-  <si>
-    <t>puissance x segment</t>
-  </si>
-  <si>
-    <t>puissance x garantie</t>
-  </si>
-  <si>
-    <t>puissance x categorie_mère</t>
-  </si>
-  <si>
-    <t>places x typepermis</t>
-  </si>
-  <si>
     <t>y_cible x typeinter</t>
   </si>
   <si>
-    <t>y_cible x type_vehicule</t>
-  </si>
-  <si>
-    <t>y_cible x segment</t>
-  </si>
-  <si>
-    <t>y_cible x categorie_mère</t>
-  </si>
-  <si>
-    <t>puissance x typepermis</t>
-  </si>
-  <si>
-    <t>puissance x type_vehicule</t>
-  </si>
-  <si>
-    <t>y_cible x garantie</t>
-  </si>
-  <si>
-    <t>puissance x typeinter</t>
-  </si>
-  <si>
-    <t>y_cible x typepermis</t>
+    <t>nb_sinistres x segment</t>
+  </si>
+  <si>
+    <t>cout_total_sinistres x segment</t>
+  </si>
+  <si>
+    <t>nb_sinistres x type_vehicule</t>
+  </si>
+  <si>
+    <t>cout_total_sinistres x type_vehicule</t>
+  </si>
+  <si>
+    <t>nb_sinistres x categorie_mère</t>
+  </si>
+  <si>
+    <t>cout_total_sinistres x categorie_mère</t>
   </si>
   <si>
     <t>duree_garantie_jours x typepermis</t>
   </si>
   <si>
-    <t>places x garantie</t>
-  </si>
-  <si>
-    <t>duree_garantie_jours x typeinter</t>
-  </si>
-  <si>
-    <t>age_vehicule_annees x typeinter</t>
-  </si>
-  <si>
-    <t>places x typeinter</t>
+    <t>cout_total_sinistres x typepermis</t>
+  </si>
+  <si>
+    <t>nb_sinistres x typepermis</t>
   </si>
   <si>
     <t>Lien significatif (p &lt; 0.05)</t>
+  </si>
+  <si>
+    <t>Indépendance (Non significatif)</t>
   </si>
 </sst>
 </file>
@@ -476,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -498,13 +558,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>26112.06294935688</v>
+        <v>4189.566222101956</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -512,13 +572,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>13310.00857715595</v>
+        <v>5058.408826071001</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -526,13 +586,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>9808.519933675409</v>
+        <v>2110.194452822195</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -540,13 +600,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>10506.88666606268</v>
+        <v>3811.042243239758</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -554,13 +614,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>2315.238747239353</v>
+        <v>3604.120719879226</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -568,13 +628,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>7631.303218803591</v>
+        <v>2071.921368696768</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -582,13 +642,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>4723.379357025642</v>
+        <v>2055.515764554209</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -596,13 +656,13 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>1653.381338944621</v>
+        <v>2392.457246670445</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -610,13 +670,13 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>28989.70308772306</v>
+        <v>1424.328614885143</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>9.177405256668783E-293</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -624,13 +684,13 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>1870.853497849263</v>
+        <v>616.0644611043666</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>7.985169289935007E-130</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -638,13 +698,13 @@
         <v>14</v>
       </c>
       <c r="B12">
-        <v>29941.28531530036</v>
+        <v>583.5364971692762</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1.93490499213737E-127</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -652,13 +712,13 @@
         <v>15</v>
       </c>
       <c r="B13">
-        <v>25268.89698740754</v>
+        <v>560.0174319049785</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>8.774155420288676E-119</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -666,13 +726,13 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>25708.52616803548</v>
+        <v>464.4921624062001</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1.370277383835384E-101</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -680,13 +740,13 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>4971.102038543046</v>
+        <v>516.2027766295681</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>7.277466053554175E-99</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -694,13 +754,13 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>17848.6321595435</v>
+        <v>467.8520017288865</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>5.519431290116944E-96</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -708,13 +768,13 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>9188.677574331328</v>
+        <v>1579.959872734333</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1.128724723164016E-80</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -722,13 +782,13 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>2466.734607586394</v>
+        <v>335.7359048655452</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1.000946577628136E-67</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -736,13 +796,13 @@
         <v>21</v>
       </c>
       <c r="B19">
-        <v>4341.413073765741</v>
+        <v>275.6889010438549</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1.364318528859584E-60</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -750,13 +810,13 @@
         <v>22</v>
       </c>
       <c r="B20">
-        <v>4195.836333525972</v>
+        <v>302.6043484214316</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>3.264899496368858E-54</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -764,13 +824,13 @@
         <v>23</v>
       </c>
       <c r="B21">
-        <v>26348.25378942016</v>
+        <v>255.2679579963238</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>3.068844445788898E-52</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -778,13 +838,13 @@
         <v>24</v>
       </c>
       <c r="B22">
-        <v>5136.707022395223</v>
+        <v>257.4439739173823</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>4.546934580047066E-51</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -792,13 +852,13 @@
         <v>25</v>
       </c>
       <c r="B23">
-        <v>18254.8664788119</v>
+        <v>278.09660509878</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>3.65202133011768E-49</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -806,13 +866,13 @@
         <v>26</v>
       </c>
       <c r="B24">
-        <v>38127.58836418964</v>
+        <v>277.7633191231789</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>4.27591166535191E-49</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -820,13 +880,13 @@
         <v>27</v>
       </c>
       <c r="B25">
-        <v>1021.179732464605</v>
+        <v>233.7847529566744</v>
       </c>
       <c r="C25">
-        <v>1.79324066858083E-222</v>
+        <v>1.651543387780364E-48</v>
       </c>
       <c r="D25" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -834,13 +894,13 @@
         <v>28</v>
       </c>
       <c r="B26">
-        <v>896.2816878438006</v>
+        <v>254.5662087432031</v>
       </c>
       <c r="C26">
-        <v>2.391341648921799E-190</v>
+        <v>2.434382994965917E-44</v>
       </c>
       <c r="D26" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -848,13 +908,13 @@
         <v>29</v>
       </c>
       <c r="B27">
-        <v>883.3690912643681</v>
+        <v>180.5125628820368</v>
       </c>
       <c r="C27">
-        <v>1.479108497203027E-187</v>
+        <v>2.281890846425922E-29</v>
       </c>
       <c r="D27" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -862,13 +922,13 @@
         <v>30</v>
       </c>
       <c r="B28">
-        <v>756.44038076563</v>
+        <v>127.530310852225</v>
       </c>
       <c r="C28">
-        <v>5.84460170045859E-149</v>
+        <v>7.953520586550624E-26</v>
       </c>
       <c r="D28" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -876,13 +936,13 @@
         <v>31</v>
       </c>
       <c r="B29">
-        <v>641.5964566842928</v>
+        <v>122.2852371096387</v>
       </c>
       <c r="C29">
-        <v>4.776388309025025E-140</v>
+        <v>5.394605653801771E-24</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -890,13 +950,13 @@
         <v>32</v>
       </c>
       <c r="B30">
-        <v>633.1756699785996</v>
+        <v>62.84910376419327</v>
       </c>
       <c r="C30">
-        <v>3.218475640450152E-138</v>
+        <v>7.300700020654053E-13</v>
       </c>
       <c r="D30" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -904,13 +964,279 @@
         <v>33</v>
       </c>
       <c r="B31">
-        <v>402.8542162457651</v>
+        <v>69.59884714614401</v>
       </c>
       <c r="C31">
-        <v>3.321379008163926E-88</v>
+        <v>5.906273133969486E-12</v>
       </c>
       <c r="D31" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
         <v>34</v>
+      </c>
+      <c r="B32">
+        <v>68.3128050508014</v>
+      </c>
+      <c r="C32">
+        <v>1.064137371814082E-11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33">
+        <v>49.63952510001637</v>
+      </c>
+      <c r="C33">
+        <v>1.663083605627444E-11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34">
+        <v>901.8034955541613</v>
+      </c>
+      <c r="C34">
+        <v>4.85304576051682E-11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35">
+        <v>901.7588767035579</v>
+      </c>
+      <c r="C35">
+        <v>4.885140337123965E-11</v>
+      </c>
+      <c r="D35" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36">
+        <v>49.6624931311331</v>
+      </c>
+      <c r="C36">
+        <v>4.246899684344256E-10</v>
+      </c>
+      <c r="D36" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37">
+        <v>49.16804855928601</v>
+      </c>
+      <c r="C37">
+        <v>5.385955625014339E-10</v>
+      </c>
+      <c r="D37" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38">
+        <v>33.0202207891824</v>
+      </c>
+      <c r="C38">
+        <v>6.756941517006762E-08</v>
+      </c>
+      <c r="D38" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39">
+        <v>32.92403526834048</v>
+      </c>
+      <c r="C39">
+        <v>7.089842385650024E-08</v>
+      </c>
+      <c r="D39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40">
+        <v>36.13355181933714</v>
+      </c>
+      <c r="C40">
+        <v>2.716290276664958E-07</v>
+      </c>
+      <c r="D40" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41">
+        <v>19.34935476031881</v>
+      </c>
+      <c r="C41">
+        <v>6.28551691705677E-05</v>
+      </c>
+      <c r="D41" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42">
+        <v>8.272128648296915</v>
+      </c>
+      <c r="C42">
+        <v>0.141862084742082</v>
+      </c>
+      <c r="D42" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43">
+        <v>8.198420379962352</v>
+      </c>
+      <c r="C43">
+        <v>0.1456340072256777</v>
+      </c>
+      <c r="D43" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44">
+        <v>7.099520400570604</v>
+      </c>
+      <c r="C44">
+        <v>0.3117416523409892</v>
+      </c>
+      <c r="D44" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45">
+        <v>7.087761563768955</v>
+      </c>
+      <c r="C45">
+        <v>0.3128073113020595</v>
+      </c>
+      <c r="D45" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46">
+        <v>8.897360783396028</v>
+      </c>
+      <c r="C46">
+        <v>0.3510284009093175</v>
+      </c>
+      <c r="D46" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47">
+        <v>8.843663109444034</v>
+      </c>
+      <c r="C47">
+        <v>0.355655645724972</v>
+      </c>
+      <c r="D47" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48">
+        <v>2.990051326314117</v>
+      </c>
+      <c r="C48">
+        <v>0.5594916652231301</v>
+      </c>
+      <c r="D48" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49">
+        <v>2.143544446618655</v>
+      </c>
+      <c r="C49">
+        <v>0.7093772292301704</v>
+      </c>
+      <c r="D49" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50">
+        <v>2.12232559437148</v>
+      </c>
+      <c r="C50">
+        <v>0.7132719541067536</v>
+      </c>
+      <c r="D50" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
